--- a/data/trans_bre/P19C01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19C01-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 11,41</t>
+          <t>-3,26; 12,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 17,64</t>
+          <t>1,43; 17,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 9,21</t>
+          <t>-5,02; 9,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 5,13</t>
+          <t>-7,02; 4,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 33,59</t>
+          <t>-8,17; 38,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 53,38</t>
+          <t>3,31; 53,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 18,93</t>
+          <t>-9,27; 20,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 7,93</t>
+          <t>-9,91; 6,94</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 14,45</t>
+          <t>-0,75; 14,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 16,41</t>
+          <t>0,87; 16,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 15,45</t>
+          <t>-0,54; 15,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 8,35</t>
+          <t>-4,31; 8,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 54,76</t>
+          <t>-1,84; 55,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 49,67</t>
+          <t>2,52; 52,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 36,69</t>
+          <t>-1,0; 37,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 13,22</t>
+          <t>-6,15; 13,09</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 17,22</t>
+          <t>-1,04; 17,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 13,53</t>
+          <t>-0,8; 13,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 6,39</t>
+          <t>-12,9; 6,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 46,02</t>
+          <t>-3,46; 47,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 69,19</t>
+          <t>-3,41; 72,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 56,31</t>
+          <t>-2,83; 56,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 18,01</t>
+          <t>-32,73; 17,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 386,09</t>
+          <t>-5,89; 368,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 13,88</t>
+          <t>4,41; 14,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 16,19</t>
+          <t>7,05; 16,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 8,14</t>
+          <t>-1,97; 8,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 10,14</t>
+          <t>-27,81; 10,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 61,11</t>
+          <t>16,2; 61,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,51; 75,53</t>
+          <t>26,44; 72,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 25,02</t>
+          <t>-4,99; 24,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,72; 19,85</t>
+          <t>-51,98; 20,33</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 7,79</t>
+          <t>-6,94; 7,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 10,69</t>
+          <t>-0,63; 10,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 13,94</t>
+          <t>1,44; 13,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 18,05</t>
+          <t>-2,86; 16,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 33,84</t>
+          <t>-20,2; 29,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 60,83</t>
+          <t>-3,14; 57,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 51,89</t>
+          <t>4,08; 50,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 41,1</t>
+          <t>-5,91; 39,23</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,28; -11,29</t>
+          <t>-27,01; -12,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,13; -10,78</t>
+          <t>-25,96; -10,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -3,19</t>
+          <t>-18,27; -3,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 4,66</t>
+          <t>-18,7; 3,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,92; -29,13</t>
+          <t>-52,57; -30,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,08; -23,79</t>
+          <t>-45,35; -23,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,98; -6,79</t>
+          <t>-30,1; -6,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 8,53</t>
+          <t>-24,82; 6,4</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,06</t>
+          <t>-1,17; 4,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,25</t>
+          <t>2,59; 7,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,57</t>
+          <t>0,2; 5,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 14,95</t>
+          <t>-5,42; 13,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 14,24</t>
+          <t>-3,71; 14,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,62; 25,9</t>
+          <t>8,4; 26,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 14,21</t>
+          <t>0,5; 13,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 33,36</t>
+          <t>-9,79; 31,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19C01-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-1,49%</t>
+          <t>-1,29%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 12,64</t>
+          <t>-2,83; 12,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 17,31</t>
+          <t>1,47; 17,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 9,42</t>
+          <t>-5,66; 9,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 4,48</t>
+          <t>-6,47; 4,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 38,05</t>
+          <t>-6,82; 36,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 53,47</t>
+          <t>3,6; 52,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 20,49</t>
+          <t>-10,43; 20,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 6,94</t>
+          <t>-9,31; 7,48</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 14,89</t>
+          <t>-1,09; 14,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 16,66</t>
+          <t>1,27; 16,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 15,48</t>
+          <t>-0,49; 15,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 8,28</t>
+          <t>-2,45; 10,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 55,52</t>
+          <t>-3,23; 54,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 52,48</t>
+          <t>3,04; 50,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 37,44</t>
+          <t>-0,93; 36,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 13,09</t>
+          <t>-3,65; 16,58</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,12</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 17,66</t>
+          <t>-1,14; 17,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 13,76</t>
+          <t>-1,17; 13,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 6,05</t>
+          <t>-13,64; 5,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 47,0</t>
+          <t>-7,13; 8,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 72,7</t>
+          <t>-3,54; 69,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 56,96</t>
+          <t>-3,78; 57,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 17,97</t>
+          <t>-34,6; 14,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 368,85</t>
+          <t>-12,18; 15,53</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>8,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-7,92%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 14,01</t>
+          <t>4,11; 13,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 16,09</t>
+          <t>6,94; 16,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 8,26</t>
+          <t>-2,4; 8,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 10,35</t>
+          <t>4,01; 12,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,2; 61,71</t>
+          <t>15,5; 59,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,44; 72,17</t>
+          <t>27,89; 73,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 24,43</t>
+          <t>-6,26; 23,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 20,33</t>
+          <t>7,35; 25,02</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 7,18</t>
+          <t>-6,67; 7,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 10,5</t>
+          <t>-0,65; 10,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,6</t>
+          <t>0,53; 13,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 16,71</t>
+          <t>0,82; 12,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 29,96</t>
+          <t>-19,91; 34,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 57,56</t>
+          <t>-2,55; 59,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 50,83</t>
+          <t>1,28; 51,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 39,23</t>
+          <t>1,66; 30,31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-8,04</t>
+          <t>-7,58</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-12,22%</t>
+          <t>-11,58%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,01; -12,16</t>
+          <t>-25,47; -11,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,96; -10,58</t>
+          <t>-27,08; -11,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -3,15</t>
+          <t>-17,72; -3,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 3,42</t>
+          <t>-18,19; 3,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,57; -30,99</t>
+          <t>-51,27; -30,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,35; -23,08</t>
+          <t>-47,22; -26,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,1; -6,33</t>
+          <t>-29,56; -7,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 6,4</t>
+          <t>-24,49; 6,62</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,01</t>
+          <t>-0,9; 4,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,43</t>
+          <t>2,37; 7,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 5,21</t>
+          <t>0,09; 5,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 13,97</t>
+          <t>0,19; 4,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 14,22</t>
+          <t>-2,9; 14,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,4; 26,54</t>
+          <t>7,79; 26,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 13,22</t>
+          <t>0,22; 14,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 31,48</t>
+          <t>0,34; 8,88</t>
         </is>
       </c>
     </row>
